--- a/input/Database.xlsx
+++ b/input/Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a286a/Documents/00_Git/VinylDatabase/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BF1254-5E34-C947-ACCC-006BC710A489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B42EAE-95FA-5C4A-9212-BD1AB2709472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="17200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Collection" sheetId="1" r:id="rId1"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>77</v>
@@ -5601,7 +5601,7 @@
         <v>123</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>44</v>
@@ -11442,3177 +11442,1938 @@
   <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="36.0" customWidth="1"/>
-    <col min="2" max="2" width="27.0" customWidth="1"/>
-    <col min="3" max="3" width="25.0" customWidth="1"/>
-    <col min="4" max="4" width="65.0" customWidth="1"/>
-    <col min="5" max="5" width="19.0" customWidth="1"/>
-    <col min="6" max="6" width="36.0" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" t="inlineStr" s="6">
-        <is>
-          <t>Artist</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="9">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="9">
-        <is>
-          <t>Subgenre</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="6">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="9">
-        <is>
-          <t>Mood</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Shelf_Band</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" t="inlineStr" s="3">
-        <is>
-          <t>Adrian Quesada</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr" s="1">
-        <is>
-          <t>Soul</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr" s="1">
-        <is>
-          <t>Intimate</t>
-        </is>
-      </c>
-      <c r="F2"/>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr" s="3">
-        <is>
-          <t>Al Di Meola, John Macluagly, Paco De Lucia</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr" s="1">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F3"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr" s="3">
-        <is>
-          <t>The Alan Parsons Project</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr" s="1">
-        <is>
-          <t>Art Rock</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Expansive or atmospheric music suited to absorbed listening.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F4"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr" s="3">
-        <is>
-          <t>The Allman Brothers Band</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr" s="1">
-        <is>
-          <t>Blues Rock</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr" s="3">
-        <is>
-          <t>Amy Winehouse</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr" s="1">
-        <is>
-          <t>Soul</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr" s="1">
-        <is>
-          <t>Melancholic</t>
-        </is>
-      </c>
-      <c r="F6"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr" s="3">
-        <is>
-          <t>Arctic Monkeys</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr" s="1">
-        <is>
-          <t>Alternative Rock</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Intense.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F7"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr" s="3">
-        <is>
-          <t>B.B. King &amp; Eric Clapton</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F8"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" t="inlineStr" s="3">
-        <is>
-          <t>Barricada</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F9"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr" s="3">
-        <is>
-          <t>The Beach Boys</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr" s="1">
-        <is>
-          <t>Art Pop</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr" s="1">
-        <is>
-          <t>Melancholic</t>
-        </is>
-      </c>
-      <c r="F10"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr" s="3">
-        <is>
-          <t>The Beatles</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr" s="1">
-        <is>
-          <t>Pop Rock</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F11"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr" s="3">
-        <is>
-          <t>Big Brother And The Holding Company</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr" s="1">
-        <is>
-          <t>Blues Rock</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F12"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr" s="3">
-        <is>
-          <t>Bob Dylan</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr" s="1">
-        <is>
-          <t>Folk</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F13"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr" s="3">
-        <is>
-          <t>Buddy Guy</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F14"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr" s="3">
-        <is>
-          <t>Buddy Holly</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr" s="1">
-        <is>
-          <t>Rock and Roll</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Relaxed, welcoming or soulful.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F15"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr" s="3">
-        <is>
-          <t>C. Tangana</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr" s="1">
-        <is>
-          <t>Latin Pop</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Pop / Warm.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" t="inlineStr" s="3">
-        <is>
-          <t>Cala Vento</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr" s="1">
-        <is>
-          <t>Alternative Rock</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F17"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr" s="3">
-        <is>
-          <t>Camaron De La Isla Y Tomatito</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr" s="1">
-        <is>
-          <t>Flamenco</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F18"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr" s="3">
-        <is>
-          <t>Casiopea</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr" s="1">
-        <is>
-          <t>Jazz Fusion</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F19"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr" s="3">
-        <is>
-          <t>Cat Stevens</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr" s="1">
-        <is>
-          <t>Folk Rock</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F20"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr" s="3">
-        <is>
-          <t>Chicano Batman</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr" s="1">
-        <is>
-          <t>Soul</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Groovy.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F21"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr" s="3">
-        <is>
-          <t>The Clash</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr" s="1">
-        <is>
-          <t>Punk Rock</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F22"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr" s="3">
-        <is>
-          <t>Daft Punk</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr" s="1">
-        <is>
-          <t>Electronic</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr" s="1">
-        <is>
-          <t>Dance Electronic</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F23"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr" s="3">
-        <is>
-          <t>David Carrol</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr" s="1">
-        <is>
-          <t>Easy Listening</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Relaxed, welcoming or soulful.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr" s="3">
-        <is>
-          <t>The Decemberists</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr" s="1">
-        <is>
-          <t>Folk Rock</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr" s="3">
-        <is>
-          <t>Deep Purple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr" s="3">
-        <is>
-          <t>Dire Straits</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr" s="1">
-        <is>
-          <t>Roots Rock</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr" s="3">
-        <is>
-          <t>Divino Nino</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr" s="1">
-        <is>
-          <t>Art Pop</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Groovy.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr" s="3">
-        <is>
-          <t>The Doors</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr" s="1">
-        <is>
-          <t>Psychedelic Rock</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F29"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr" s="3">
-        <is>
-          <t>Eagles</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr" s="1">
-        <is>
-          <t>Roots Rock</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F30"/>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr" s="3">
-        <is>
-          <t>Edith Piaf</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr" s="1">
-        <is>
-          <t>Vocal</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Jazz / Blues / Intense.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F31"/>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr" s="3">
-        <is>
-          <t>El Ultimo De La Fila</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr" s="1">
-        <is>
-          <t>Pop Rock</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Intense.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F32"/>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr" s="3">
-        <is>
-          <t>Elliot Smith</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr" s="1">
-        <is>
-          <t>Folk Rock</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr" s="1">
-        <is>
-          <t>Melancholic</t>
-        </is>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr" s="3">
-        <is>
-          <t>Els Pets</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr" s="1">
-        <is>
-          <t>Pop Rock</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr" s="3">
-        <is>
-          <t>Elton John</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr" s="1">
-        <is>
-          <t>Pop Rock</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Pop / Warm.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F35"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" t="inlineStr" s="3">
-        <is>
-          <t>Emerson Lake And Palmer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr" s="1">
-        <is>
-          <t>Progressive Rock</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Expansive or atmospheric music suited to absorbed listening.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F36"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr" s="3">
-        <is>
-          <t>Eric Clapton</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr" s="1">
-        <is>
-          <t>Intimate</t>
-        </is>
-      </c>
-      <c r="F37"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr" s="3">
-        <is>
-          <t>Extremoduro</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F38"/>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr" s="3">
-        <is>
-          <t>Fats Domino</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr" s="1">
-        <is>
-          <t>Rock and Roll</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F39"/>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr" s="3">
-        <is>
-          <t>Frank Sinatra</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr" s="1">
-        <is>
-          <t>Vocal</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F40"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr" s="3">
-        <is>
-          <t>Gorillaz</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr" s="1">
-        <is>
-          <t>Electronic</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr" s="1">
-        <is>
-          <t>Electronic Pop</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F41"/>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr" s="3">
-        <is>
-          <t>Greta Van Fleet</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F42"/>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr" s="3">
-        <is>
-          <t>Guns N' Roses</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F43"/>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" t="inlineStr" s="3">
-        <is>
-          <t>Henry Mancini</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr" s="1">
-        <is>
-          <t>Soundtrack</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Relaxed, welcoming or soulful.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F44"/>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" t="inlineStr" s="3">
-        <is>
-          <t>Iggy Pop</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr" s="1">
-        <is>
-          <t>Art Rock</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F45"/>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" t="inlineStr" s="3">
-        <is>
-          <t>Janis Joplin</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr" s="1">
-        <is>
-          <t>Blues Rock</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Big Brother And The Holding Company</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" t="inlineStr" s="3">
-        <is>
-          <t>Jimi Hendrix</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr" s="1">
-        <is>
-          <t>Psychedelic Rock</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F47"/>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" t="inlineStr" s="3">
-        <is>
-          <t>Joe Hisaishi</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr" s="1">
-        <is>
-          <t>Soundtrack</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F48"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" t="inlineStr" s="3">
-        <is>
-          <t>John Lee Hooker</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr" s="1">
-        <is>
-          <t>Intimate</t>
-        </is>
-      </c>
-      <c r="F49"/>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" t="inlineStr" s="3">
-        <is>
-          <t>John Mayall</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F50"/>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" t="inlineStr" s="3">
-        <is>
-          <t>John Mayall And The Blues Breakers</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F51"/>
-    </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" t="inlineStr" s="3">
-        <is>
-          <t>Johnny Cash</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr" s="1">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F52"/>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" t="inlineStr" s="3">
-        <is>
-          <t>Kase-O</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr" s="1">
-        <is>
-          <t>Jazz Rap</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F53"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" t="inlineStr" s="3">
-        <is>
-          <t>King Crimson</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr" s="1">
-        <is>
-          <t>Progressive Rock</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Expansive or atmospheric music suited to absorbed listening.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F54"/>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" t="inlineStr" s="3">
-        <is>
-          <t>Konami</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr" s="1">
-        <is>
-          <t>Soundtrack</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Classical / Soundtrack / Immersive.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F55"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" t="inlineStr" s="3">
-        <is>
-          <t>Lana Del Rey</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr" s="1">
-        <is>
-          <t>Art Pop</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr" s="1">
-        <is>
-          <t>Melancholic</t>
-        </is>
-      </c>
-      <c r="F56"/>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" t="inlineStr" s="3">
-        <is>
-          <t>Led Zeppelin</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr" s="1">
-        <is>
-          <t>Blues Rock</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F57"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" t="inlineStr" s="3">
-        <is>
-          <t>Lisa Batiashvili</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr" s="1">
-        <is>
-          <t>Classical</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F58"/>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" t="inlineStr" s="3">
-        <is>
-          <t>Los Burros</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr" s="1">
-        <is>
-          <t>Pop Rock</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Intense.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F59"/>
-    </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" t="inlineStr" s="3">
-        <is>
-          <t>Lou Reed</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr" s="1">
-        <is>
-          <t>Glam Rock</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>The Velvet Underground &amp; Nico</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" t="inlineStr" s="3">
-        <is>
-          <t>Ludwig Van Beethoven</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr" s="1">
-        <is>
-          <t>Classical</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Classical / Soundtrack / Immersive.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F61"/>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" t="inlineStr" s="3">
-        <is>
-          <t>Madness</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr" s="1">
-        <is>
-          <t>Ska</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F62"/>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" t="inlineStr" s="3">
-        <is>
-          <t>Manel</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr" s="1">
-        <is>
-          <t>Electronic Pop</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F63"/>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" t="inlineStr" s="3">
-        <is>
-          <t>Maria Del Mar Bonet</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr" s="1">
-        <is>
-          <t>Folk</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Jazz / Blues; mood: Melancholic.</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr" s="1">
-        <is>
-          <t>Melancholic</t>
-        </is>
-      </c>
-      <c r="F64"/>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" t="inlineStr" s="3">
-        <is>
-          <t>Masayoshi Takanaka</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr" s="1">
-        <is>
-          <t>Jazz Fusion</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F65"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" t="inlineStr" s="3">
-        <is>
-          <t>Max Richter</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr" s="1">
-        <is>
-          <t>Classical</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F66"/>
-    </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" t="inlineStr" s="3">
-        <is>
-          <t>Muddy Waters</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F67"/>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" t="inlineStr" s="3">
-        <is>
-          <t>Muddy Waters &amp; The Rolling Stones</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F68"/>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" t="inlineStr" s="3">
-        <is>
-          <t>Natalia Lafourcade</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr" s="1">
-        <is>
-          <t>Folk</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F69"/>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" t="inlineStr" s="3">
-        <is>
-          <t>New Orlenad Sweet Emma And Her Preservation Hall Jazz Band</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr" s="1">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F70"/>
-    </row>
-    <row r="71" ht="32" customHeight="1">
-      <c r="A71" t="inlineStr" s="3">
-        <is>
-          <t>Nick Mason</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr" s="1">
-        <is>
-          <t>Psychedelic Rock</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Pink Floyd</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" t="inlineStr" s="3">
-        <is>
-          <t>Nirvana</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr" s="1">
-        <is>
-          <t>Acoustic Rock</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F72"/>
-    </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" t="inlineStr" s="3">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr" s="1">
-        <is>
-          <t>Jazz Fusion</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F73"/>
-    </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" t="inlineStr" s="3">
-        <is>
-          <t>Paco And John</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr" s="1">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F74"/>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" t="inlineStr" s="3">
-        <is>
-          <t>Paco De Lucia</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr" s="1">
-        <is>
-          <t>Flamenco</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F75"/>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" t="inlineStr" s="3">
-        <is>
-          <t>Parcels</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr" s="1">
-        <is>
-          <t>Disco</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Groovy.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F76"/>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" t="inlineStr" s="3">
-        <is>
-          <t>Patti Smith</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr" s="1">
-        <is>
-          <t>Punk Rock</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F77"/>
-    </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" t="inlineStr" s="3">
-        <is>
-          <t>Paul Mccartney</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr" s="1">
-        <is>
-          <t>Folk Rock</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr" s="1">
-        <is>
-          <t>Intimate</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>The Beatles</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" t="inlineStr" s="3">
-        <is>
-          <t>Pearl Jam</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr" s="1">
-        <is>
-          <t>Alternative Rock</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F79"/>
-    </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" t="inlineStr" s="3">
-        <is>
-          <t>Pink Floyd</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr" s="1">
-        <is>
-          <t>Progressive Rock</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F80"/>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" t="inlineStr" s="3">
-        <is>
-          <t>The Prodigy</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr" s="1">
-        <is>
-          <t>Electronic</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr" s="1">
-        <is>
-          <t>Dance Electronic</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F81"/>
-    </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" t="inlineStr" s="3">
-        <is>
-          <t>Queen</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr" s="1">
-        <is>
-          <t>Art Rock</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Intense.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F82"/>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" t="inlineStr" s="3">
-        <is>
-          <t>Queens Of The Stone Age</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr" s="1">
-        <is>
-          <t>Alternative Rock</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F83"/>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" t="inlineStr" s="3">
-        <is>
-          <t>Radiohead</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr" s="1">
-        <is>
-          <t>Art Rock</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr" s="1">
-        <is>
-          <t>Melancholic</t>
-        </is>
-      </c>
-      <c r="F84"/>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" t="inlineStr" s="3">
-        <is>
-          <t>Rage Against The Machine</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F85"/>
-    </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" t="inlineStr" s="3">
-        <is>
-          <t>Rainbow</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Forceful, urgent or hard-driving.</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F86"/>
-    </row>
-    <row r="87" ht="32" customHeight="1">
-      <c r="A87" t="inlineStr" s="3">
-        <is>
-          <t>Red Hot Chili Peppers</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr" s="1">
-        <is>
-          <t>Funk Rock</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F87"/>
-    </row>
-    <row r="88" ht="32" customHeight="1">
-      <c r="A88" t="inlineStr" s="3">
-        <is>
-          <t>Rigoberta Bandini</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr" s="1">
-        <is>
-          <t>Pop</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr" s="1">
-        <is>
-          <t>Electronic Pop</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F88"/>
-    </row>
-    <row r="89" ht="32" customHeight="1">
-      <c r="A89" t="inlineStr" s="3">
-        <is>
-          <t>Robe</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr" s="1">
-        <is>
-          <t>Art Rock</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Intense.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Extremoduro</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="32" customHeight="1">
-      <c r="A90" t="inlineStr" s="3">
-        <is>
-          <t>Roger Waters</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr" s="1">
-        <is>
-          <t>Progressive Rock</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Pink Floyd</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="32" customHeight="1">
-      <c r="A91" t="inlineStr" s="3">
-        <is>
-          <t>The Rolling Stones</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F91"/>
-    </row>
-    <row r="92" ht="32" customHeight="1">
-      <c r="A92" t="inlineStr" s="3">
-        <is>
-          <t>Rory Gallagher</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr" s="1">
-        <is>
-          <t>Blues Rock</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F92"/>
-    </row>
-    <row r="93" ht="32" customHeight="1">
-      <c r="A93" t="inlineStr" s="3">
-        <is>
-          <t>Roy Buchannan</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F93"/>
-    </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" t="inlineStr" s="3">
-        <is>
-          <t>Santana</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr" s="1">
-        <is>
-          <t>Latin Rock</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F94"/>
-    </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" t="inlineStr" s="3">
-        <is>
-          <t>Sly And The Family Stone</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr" s="1">
-        <is>
-          <t>Funk</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F95"/>
-    </row>
-    <row r="96" ht="32" customHeight="1">
-      <c r="A96" t="inlineStr" s="3">
-        <is>
-          <t>Stevie Ray Vaughan And Double Trouble</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr" s="1">
-        <is>
-          <t>Blues</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F96"/>
-    </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" t="inlineStr" s="3">
-        <is>
-          <t>The Strokes</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr" s="1">
-        <is>
-          <t>Alternative Rock</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Forceful, urgent or hard-driving.</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F97"/>
-    </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" t="inlineStr" s="3">
-        <is>
-          <t>Studio Ghibli</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr" s="1">
-        <is>
-          <t>Soundtrack</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Expansive or atmospheric music suited to absorbed listening.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F98"/>
-    </row>
-    <row r="99" ht="32" customHeight="1">
-      <c r="A99" t="inlineStr" s="3">
-        <is>
-          <t>Supertramp</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr" s="1">
-        <is>
-          <t>Art Rock</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr" s="3">
-        <is>
-          <t>Personal shelf classification: Rock / Immersive.</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F99"/>
-    </row>
-    <row r="100" ht="32" customHeight="1">
-      <c r="A100" t="inlineStr" s="3">
-        <is>
-          <t>T. Rex</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr" s="1">
-        <is>
-          <t>Glam Rock</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr" s="3">
-        <is>
-          <t>Curated artist-level mood: Rhythm-led, with a prominent groove, swing or dance pulse.</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr" s="1">
-        <is>
-          <t>Groovy</t>
-        </is>
-      </c>
-      <c r="F100"/>
-    </row>
-    <row r="101" ht="32" customHeight="1">
-      <c r="A101" t="inlineStr" s="3">
-        <is>
-          <t>Ten Years After</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr" s="1">
-        <is>
-          <t>Blues Rock</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F101"/>
-    </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" t="inlineStr" s="3">
-        <is>
-          <t>Thin Lizzy</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F102"/>
-    </row>
-    <row r="103" ht="32" customHeight="1">
-      <c r="A103" t="inlineStr" s="3">
-        <is>
-          <t>Tony Bennet</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr" s="1">
-        <is>
-          <t>Jazz / Blues</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr" s="1">
-        <is>
-          <t>Vocal</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F103"/>
-    </row>
-    <row r="104" ht="32" customHeight="1">
-      <c r="A104" t="inlineStr" s="3">
-        <is>
-          <t>Various Artists</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr" s="1">
-        <is>
-          <t>Classical / Soundtrack</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr" s="1">
-        <is>
-          <t>Soundtrack</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F104"/>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" t="inlineStr" s="3">
-        <is>
-          <t>The Velvet Underground &amp; Nico</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr" s="1">
-        <is>
-          <t>Experimental Rock</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr" s="1">
-        <is>
-          <t>Immersive</t>
-        </is>
-      </c>
-      <c r="F105"/>
-    </row>
-    <row r="106" ht="32" customHeight="1">
-      <c r="A106" t="inlineStr" s="3">
-        <is>
-          <t>The Wailers</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr" s="1">
-        <is>
-          <t>Reggae</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F106"/>
-    </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" t="inlineStr" s="3">
-        <is>
-          <t>War Child</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr" s="1">
-        <is>
-          <t>Alternative Rock</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F107"/>
-    </row>
-    <row r="108" ht="32" customHeight="1">
-      <c r="A108" t="inlineStr" s="3">
-        <is>
-          <t>Weezer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr" s="1">
-        <is>
-          <t>Art Pop</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr" s="1">
-        <is>
-          <t>Reflective</t>
-        </is>
-      </c>
-      <c r="F108"/>
-    </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" t="inlineStr" s="3">
-        <is>
-          <t>The Who</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr" s="1">
-        <is>
-          <t>Hard Rock</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F109"/>
-    </row>
-    <row r="110" ht="32" customHeight="1">
-      <c r="A110" t="inlineStr" s="3">
-        <is>
-          <t>Woodstock</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr" s="1">
-        <is>
-          <t>Classic Rock</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F110"/>
-    </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" t="inlineStr" s="3">
-        <is>
-          <t>Woodstock Two</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr" s="1">
-        <is>
-          <t>Classic Rock</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr" s="1">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="F111"/>
-    </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" t="inlineStr" s="3">
-        <is>
-          <t>Yoko Ono</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr" s="1">
-        <is>
-          <t>Rock</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr" s="1">
-        <is>
-          <t>Experimental Rock</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr" s="3">
-        <is>
-          <t>One shared mood across this artist's records; editable.</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr" s="1">
-        <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="F112"/>
+    <row r="1" spans="1:6" ht="30" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="F1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="32" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="32" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="32" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="32" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="32" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="32" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="32" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="32" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="32" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="32" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="32" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="32" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="32" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="32" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="32" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="32" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="32" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="32" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="32" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="32" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="32" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="32" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="32" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="32" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="32" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="32" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="32" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="32" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="32" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="32" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="32" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="32" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="32" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="32" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="32" customHeight="1">
+      <c r="A43" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="32" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="32" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="32" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F46" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="32" customHeight="1">
+      <c r="A47" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="32" customHeight="1">
+      <c r="A48" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="32" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="32" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="32" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="32" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="32" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="32" customHeight="1">
+      <c r="A54" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="32" customHeight="1">
+      <c r="A55" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="32" customHeight="1">
+      <c r="A56" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="32" customHeight="1">
+      <c r="A57" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="32" customHeight="1">
+      <c r="A58" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="32" customHeight="1">
+      <c r="A59" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="32" customHeight="1">
+      <c r="A60" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F60" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="32" customHeight="1">
+      <c r="A61" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="32" customHeight="1">
+      <c r="A62" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="32" customHeight="1">
+      <c r="A63" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="32" customHeight="1">
+      <c r="A64" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="32" customHeight="1">
+      <c r="A65" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="32" customHeight="1">
+      <c r="A66" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="32" customHeight="1">
+      <c r="A67" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="32" customHeight="1">
+      <c r="A68" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="32" customHeight="1">
+      <c r="A69" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="32" customHeight="1">
+      <c r="A70" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="32" customHeight="1">
+      <c r="A71" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F71" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="32" customHeight="1">
+      <c r="A72" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="32" customHeight="1">
+      <c r="A73" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="32" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="32" customHeight="1">
+      <c r="A75" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="32" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="32" customHeight="1">
+      <c r="A77" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="32" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="F78" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="32" customHeight="1">
+      <c r="A79" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="32" customHeight="1">
+      <c r="A80" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="32" customHeight="1">
+      <c r="A81" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="32" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="32" customHeight="1">
+      <c r="A83" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="32" customHeight="1">
+      <c r="A84" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="32" customHeight="1">
+      <c r="A85" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="32" customHeight="1">
+      <c r="A86" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="32" customHeight="1">
+      <c r="A87" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="32" customHeight="1">
+      <c r="A88" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="32" customHeight="1">
+      <c r="A89" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F89" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="32" customHeight="1">
+      <c r="A90" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="F90" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="32" customHeight="1">
+      <c r="A91" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="32" customHeight="1">
+      <c r="A92" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="32" customHeight="1">
+      <c r="A93" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="32" customHeight="1">
+      <c r="A94" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="32" customHeight="1">
+      <c r="A95" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="32" customHeight="1">
+      <c r="A96" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="32" customHeight="1">
+      <c r="A97" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="32" customHeight="1">
+      <c r="A98" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="32" customHeight="1">
+      <c r="A99" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="32" customHeight="1">
+      <c r="A100" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="32" customHeight="1">
+      <c r="A101" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="32" customHeight="1">
+      <c r="A102" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="32" customHeight="1">
+      <c r="A103" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="32" customHeight="1">
+      <c r="A104" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="32" customHeight="1">
+      <c r="A105" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="32" customHeight="1">
+      <c r="A106" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="32" customHeight="1">
+      <c r="A107" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="32" customHeight="1">
+      <c r="A108" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="32" customHeight="1">
+      <c r="A109" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="32" customHeight="1">
+      <c r="A110" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="32" customHeight="1">
+      <c r="A111" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="32" customHeight="1">
+      <c r="A112" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>744</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
